--- a/input/06_input_bukti_terima_paket_internet.xlsx
+++ b/input/06_input_bukti_terima_paket_internet.xlsx
@@ -54,7 +54,7 @@
     <t>BY.U</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1RT8OyS7hbilVLkcNZ2a77mwE-GtpsYlC</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>63041520030XXXXX</t>
@@ -72,7 +72,7 @@
     <t>TELKOMSEL</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1kDaNcYFgx4Qh-VEU4c3ElNGcqIJHT8So</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>63040246109XXXXX</t>
@@ -90,7 +90,7 @@
     <t>AXIS</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1WZsqRHl-ZUbNkYTBOhMdoP8JGUBf0x37</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>63040215090XXXXX</t>
@@ -102,7 +102,7 @@
     <t>Keenan Tee</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1cvxtJm-iTwlEvncn4sDN1zkz4Jdr1Mi8</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>63040128080XXXXX</t>
@@ -117,7 +117,7 @@
     <t>[010] TABUNGANEN</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1lHq5-Z_IhIqJdCGKezCsBYrLOF1gRzc7</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>63040248069XXXXX</t>
@@ -132,7 +132,7 @@
     <t>THREE/3</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1D5XOJN8SVq7C6-AzsHU9RhFtEevHYU6M</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>63041668069XXXXX</t>
@@ -150,7 +150,7 @@
     <t>INDOSAT</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=18QyZyxZtuMIaemBbJSxPXwPh4sbDsAnJ</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>63040419129XXXXX</t>
@@ -162,7 +162,7 @@
     <t>Feby Putri</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1Kw9Q-NXmR7-pYGrThgs7dHg44Rnf8hqj</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>nama_lengkap</t>
